--- a/outputs/Block2_Nested_LOEO_Details_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Details_v12.xlsx
@@ -642,7 +642,7 @@
         <v>0.4885960000000001</v>
       </c>
       <c r="G5">
-        <v>0.03440399999999993</v>
+        <v>0.03440399999999988</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -665,7 +665,7 @@
         <v>0.4995673824154764</v>
       </c>
       <c r="G6">
-        <v>0.02343261758452359</v>
+        <v>0.02343261758452364</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -846,10 +846,10 @@
         <v>0.443</v>
       </c>
       <c r="F14">
-        <v>0.4761983181443601</v>
+        <v>0.47619831814436</v>
       </c>
       <c r="G14">
-        <v>0.03319831814436008</v>
+        <v>0.03319831814436003</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -5400,10 +5400,10 @@
         <v>0.449</v>
       </c>
       <c r="F212">
-        <v>0.4773119999999992</v>
+        <v>0.4773119999999993</v>
       </c>
       <c r="G212">
-        <v>0.02831199999999923</v>
+        <v>0.02831199999999928</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -10230,10 +10230,10 @@
         <v>0.455</v>
       </c>
       <c r="F422">
-        <v>0.4810567147557039</v>
+        <v>0.481056714755704</v>
       </c>
       <c r="G422">
-        <v>0.02605671475570387</v>
+        <v>0.02605671475570398</v>
       </c>
     </row>
     <row r="423" spans="1:7">
@@ -10391,10 +10391,10 @@
         <v>0.512</v>
       </c>
       <c r="F429">
-        <v>0.487575999999999</v>
+        <v>0.4875759999999989</v>
       </c>
       <c r="G429">
-        <v>0.02442400000000106</v>
+        <v>0.02442400000000111</v>
       </c>
     </row>
     <row r="430" spans="1:7">
@@ -10414,10 +10414,10 @@
         <v>0.512</v>
       </c>
       <c r="F430">
-        <v>0.4895113339758256</v>
+        <v>0.4895113339758257</v>
       </c>
       <c r="G430">
-        <v>0.02248866602417443</v>
+        <v>0.02248866602417432</v>
       </c>
     </row>
     <row r="431" spans="1:7">
@@ -15014,10 +15014,10 @@
         <v>0.534</v>
       </c>
       <c r="F630">
-        <v>0.483763767479223</v>
+        <v>0.4837637674792231</v>
       </c>
       <c r="G630">
-        <v>0.05023623252077702</v>
+        <v>0.05023623252077697</v>
       </c>
     </row>
     <row r="631" spans="1:7">
@@ -15175,10 +15175,10 @@
         <v>0.448</v>
       </c>
       <c r="F637">
-        <v>0.4865799999999994</v>
+        <v>0.4865799999999995</v>
       </c>
       <c r="G637">
-        <v>0.03857999999999939</v>
+        <v>0.03857999999999945</v>
       </c>
     </row>
     <row r="638" spans="1:7">
@@ -15198,10 +15198,10 @@
         <v>0.448</v>
       </c>
       <c r="F638">
-        <v>0.4843105651824636</v>
+        <v>0.4843105651824637</v>
       </c>
       <c r="G638">
-        <v>0.03631056518246362</v>
+        <v>0.03631056518246373</v>
       </c>
     </row>
     <row r="639" spans="1:7">
@@ -19755,7 +19755,7 @@
         <v>0.4759039999999993</v>
       </c>
       <c r="G836">
-        <v>0.002903999999999352</v>
+        <v>0.002903999999999296</v>
       </c>
     </row>
     <row r="837" spans="1:7">
@@ -19798,10 +19798,10 @@
         <v>0.473</v>
       </c>
       <c r="F838">
-        <v>0.4794602172888914</v>
+        <v>0.4794602172888913</v>
       </c>
       <c r="G838">
-        <v>0.006460217288891401</v>
+        <v>0.006460217288891346</v>
       </c>
     </row>
     <row r="839" spans="1:7">
